--- a/xslope/resources/input_template.xlsx
+++ b/xslope/resources/input_template.xlsx
@@ -629,7 +629,7 @@
     <t>* piezometric line 2 is only required for rapid drawdown analysis</t>
   </si>
   <si>
-    <t>Type optons</t>
+    <t>Type options</t>
   </si>
   <si>
     <t>True piezometric line: u = γw × vertical distance below the line (static head).</t>
@@ -638,7 +638,7 @@
     <t>phreatic</t>
   </si>
   <si>
-    <t xml:space="preserve"> Phreatic surface: static head reduced by cos² of the line's slope.</t>
+    <t>Phreatic surface: static head reduced by cos² of the line's slope.</t>
   </si>
   <si>
     <t>#</t>

--- a/xslope/resources/input_template.xlsx
+++ b/xslope/resources/input_template.xlsx
@@ -12861,76 +12861,76 @@
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
